--- a/test/财务/输入附件-扩展版.xlsx
+++ b/test/财务/输入附件-扩展版.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orders" sheetId="1" r:id="Rec9261a518414b37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payments" sheetId="2" r:id="Rdd0fbd94c8d84454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="3" r:id="R69f3db22b24e4eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orders" sheetId="1" r:id="Red0c5864bbb74a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payments" sheetId="2" r:id="R9282c1fa7e034a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="3" r:id="R60857fb49b464767"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -270,6 +270,7 @@
     <ns0:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
     <ns0:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
     <ns0:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <ns0:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
   </ns0:cols>
   <ns0:sheetData>
     <ns0:row r="1" ht="15" hidden="0" customHeight="1">
@@ -282,6 +283,9 @@
       <ns0:c r="C1" s="4" t="str">
         <ns0:v>purchased_at</ns0:v>
       </ns0:c>
+      <ns0:c r="D1" s="4" t="str">
+        <ns0:v>purchased_month</ns0:v>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="2" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A2" s="2" t="inlineStr">
@@ -299,6 +303,11 @@
           <ns0:t xml:space="preserve">2018-07-05 19:41:43</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D2" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="3" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A3" s="2" t="inlineStr">
@@ -316,6 +325,11 @@
           <ns0:t xml:space="preserve">2018-08-10 16:28:54</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D3" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="4" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A4" s="2" t="inlineStr">
@@ -333,6 +347,11 @@
           <ns0:t xml:space="preserve">2017-09-15 16:48:18</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D4" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-09</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="5" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A5" s="2" t="inlineStr">
@@ -350,6 +369,11 @@
           <ns0:t xml:space="preserve">2018-08-15 18:51:47</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D5" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="6" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A6" s="2" t="inlineStr">
@@ -367,6 +391,11 @@
           <ns0:t xml:space="preserve">2017-12-15 21:53:01</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-12</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="7" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A7" s="2" t="inlineStr">
@@ -384,6 +413,11 @@
           <ns0:t xml:space="preserve">2017-02-10 19:44:25</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D7" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="8" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A8" s="2" t="inlineStr">
@@ -401,6 +435,11 @@
           <ns0:t xml:space="preserve">2018-03-27 14:29:03</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D8" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-03</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="9" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A9" s="2" t="inlineStr">
@@ -418,6 +457,11 @@
           <ns0:t xml:space="preserve">2018-03-07 11:07:38</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D9" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-03</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="10" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A10" s="2" t="inlineStr">
@@ -435,6 +479,11 @@
           <ns0:t xml:space="preserve">2017-03-13 21:30:52</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D10" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-03</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="11" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A11" s="2" t="inlineStr">
@@ -452,6 +501,11 @@
           <ns0:t xml:space="preserve">2017-04-01 13:45:09</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D11" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-04</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="12" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A12" s="2" t="inlineStr">
@@ -469,6 +523,11 @@
           <ns0:t xml:space="preserve">2017-07-04 18:48:46</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D12" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="13" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A13" s="2" t="inlineStr">
@@ -486,6 +545,11 @@
           <ns0:t xml:space="preserve">2018-01-10 15:18:58</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D13" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-01</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="14" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A14" s="2" t="inlineStr">
@@ -503,6 +567,11 @@
           <ns0:t xml:space="preserve">2017-10-23 15:38:27</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D14" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-10</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="15" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A15" s="2" t="inlineStr">
@@ -520,6 +589,11 @@
           <ns0:t xml:space="preserve">2018-03-20 10:54:13</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D15" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2018-03</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="16" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A16" s="2" t="inlineStr">
@@ -537,6 +611,11 @@
           <ns0:t xml:space="preserve">2017-09-13 18:49:58</ns0:t>
         </ns0:is>
       </ns0:c>
+      <ns0:c r="D16" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-09</ns0:t>
+        </ns0:is>
+      </ns0:c>
     </ns0:row>
     <ns0:row r="17" ht="15" hidden="0" customHeight="1">
       <ns0:c r="A17" s="2" t="inlineStr">
@@ -552,6 +631,11 @@
       <ns0:c r="C17" s="2" t="inlineStr">
         <ns0:is>
           <ns0:t xml:space="preserve">2017-03-24 22:20:26</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D17" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2017-03</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
